--- a/astro-site/public/dl/pizza-shop-checklist-templates/08-pizzeria-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/08-pizzeria-opening-closing-checklist.xlsx
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Light the wood-fired oven (preheat per manufacturer; 1 h as a guide)</t>
+          <t>Exhaust hood on, then light the oven (preheat per manufacturer; 1 h as a guide; detail in 01, Kitchen Opening)</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>9:30 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Set up the pizza counter if visible; slices (pizza by the slice) go in a hot case at 135 °F or above, or time-marked and tossed at 4 h (FDA 3-501.19)</t>
+          <t>Set up the slice counter if you sell by the slice: hot case at 135 °F or above, or time-marked and tossed at 4 h with a written procedure on file (FDA 3-501.19)</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
